--- a/语音/励磁巡检.xlsx
+++ b/语音/励磁巡检.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23145" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="1号水轮机调速器巡检" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="236">
   <si>
     <t>序号</t>
   </si>
@@ -146,27 +146,21 @@
     <t>已完成励磁调节柜空气开关检查</t>
   </si>
   <si>
-    <t>检测1号发电机励磁调节柜A套励磁调节装置，“运行”、“主从”、“投励”、“并网”、“自动运行”指示灯亮,显示屏无故障报警信息</t>
-  </si>
-  <si>
-    <t>检测1号发电机励磁调节柜A套励磁调节装置</t>
+    <t>检测1号发电机励磁调节柜A套,B套励磁调节装置,“运行”、“主从”、“投励”、“并网”、“自动运行”指示灯亮,显示屏无故障报警信息</t>
+  </si>
+  <si>
+    <t>检测1号发电机励磁调节柜A套,B套励磁调节装置</t>
   </si>
   <si>
     <t>“运行”、“主从”、“投励”、“并网”、“自动运行”指示灯亮,显示屏无故障报警信息</t>
   </si>
   <si>
+    <t>“运行”、“投励”、“并网”、“自动运行”指示灯亮,显示屏无故障报警信息</t>
+  </si>
+  <si>
     <t>已完成励磁调节柜A套励磁调节装置检查</t>
   </si>
   <si>
-    <t>检测1号发电机励磁调节柜B套励磁调节装置，“运行”、“投励”、“并网”、“自动运行”指示灯亮,显示屏无故障报警信息</t>
-  </si>
-  <si>
-    <t>检测1号发电机励磁调节柜B套励磁调节装置</t>
-  </si>
-  <si>
-    <t>“运行”、“投励”、“并网”、“自动运行”指示灯亮,显示屏无故障报警信息</t>
-  </si>
-  <si>
     <t>已完成励磁调节柜B套励磁调节装置检查</t>
   </si>
   <si>
@@ -263,7 +257,7 @@
     <t>可控硅1号整流柜巡检</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜外观，设备完好无损坏、无锈蚀，漆面无脱落、清洁无异物</t>
+    <t xml:space="preserve">检查可控硅1号整流柜外观，有电标识完好，屏柜完好无损坏、锈蚀，漆面无脱落、设备清洁 </t>
   </si>
   <si>
     <t>检查可控硅1号整流柜外观</t>
@@ -272,18 +266,12 @@
     <t>设备完好无损坏、无锈蚀，漆面无脱落、清洁无异物</t>
   </si>
   <si>
+    <t>有电标识正确完好</t>
+  </si>
+  <si>
     <t>已完成可控硅1号整流柜外观检查</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜有电标识，有电标识正确完好</t>
-  </si>
-  <si>
-    <t>检查可控硅1号整流柜有电标识</t>
-  </si>
-  <si>
-    <t>有电标识正确完好</t>
-  </si>
-  <si>
     <t>已完成可控硅1号整流柜有电标识检查</t>
   </si>
   <si>
@@ -311,16 +299,16 @@
     <t>已完成可控硅1号整流柜电流表指示检查</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置，“运行”“智能均流”指示灯点亮，显示屏无故障报警信号。</t>
-  </si>
-  <si>
-    <t>检查可控硅1号整流柜PCS-9425整流桥智能测控装置</t>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置，“运行”“智能均流”指示灯点亮，显示屏无故障报警信号。</t>
+  </si>
+  <si>
+    <t>检查可控硅1号整流柜，PCS-9425整流桥智能测控装置</t>
   </si>
   <si>
     <t>“运行”“智能均流”指示灯点亮，显示屏无故障报警信号。</t>
   </si>
   <si>
-    <t>已完成可控硅1号整流柜PCS-9425整流桥智能测控装置检查</t>
+    <t>已完成可控硅1号整流柜，PCS-9425整流桥智能测控装置检查</t>
   </si>
   <si>
     <t>检查可控硅1号整流柜整流桥风机，整流桥1号风机运转正常，无异音，冷却效果良好</t>
@@ -374,13 +362,13 @@
     <t>已完成可控硅1号整流柜柜铝母线排检测</t>
   </si>
   <si>
-    <t>检查可控硅1号整流柜接触器，“ZJ”、“AJ3”接触器吸，“AJ1”“AJ2”分位</t>
+    <t>检查可控硅1号整流柜接触器，“ZJ”、“AJ3”接触器吸合，“AJ1”“AJ2”分位</t>
   </si>
   <si>
     <t>检查可控硅1号整流柜接触器</t>
   </si>
   <si>
-    <t>“ZJ”、“AJ3”接触器吸，“AJ1”“AJ2”分位</t>
+    <t>“ZJ”、“AJ3”接触器吸合，“AJ1”“AJ2”分位</t>
   </si>
   <si>
     <t>已完成可控硅1号整流柜接触器检测</t>
@@ -524,7 +512,7 @@
     <t>检查1号发电机灭磁柜表计指示</t>
   </si>
   <si>
-    <t>励磁电流表显示值为整流柜电流值的两倍</t>
+    <t>励磁电流表显示值为整流柜电流值的两倍，与LUC柜示数一致</t>
   </si>
   <si>
     <t>已完成灭磁柜表计指示检查</t>
@@ -578,7 +566,7 @@
     <t>检查1号发电机灭磁柜分合闸控制开关</t>
   </si>
   <si>
-    <t>控制开关完好，标示清晰，在中间位置</t>
+    <t>分合闸控制开关完好，标示清晰，在中间位置</t>
   </si>
   <si>
     <t>已完成灭磁柜分合闸控制开关检查</t>
@@ -626,7 +614,7 @@
     <t>已关闭灭磁柜柜门</t>
   </si>
   <si>
-    <t>调速励磁PT及励变进线柜，励磁变压器</t>
+    <t>调速励磁PT及励变进线柜，励磁变压器巡检</t>
   </si>
   <si>
     <t>检查调速励磁PT及励变进线柜外观，柜门关闭严密，清洁无蛛网</t>
@@ -665,13 +653,13 @@
     <t>已完成励磁调速PT及励变进线柜五防锁具检查</t>
   </si>
   <si>
-    <t>检查调速励磁PT及励变进线柜电压测量表计，电压测量表计显示10KV</t>
+    <t>检查1号机调速励磁PT及励变进线柜电压测量表计，显示10kV</t>
   </si>
   <si>
     <t>检查调速励磁PT及励变进线柜电压测量表计</t>
   </si>
   <si>
-    <t>电压测量表计显示10KV</t>
+    <t>电压测量表计显示10kV</t>
   </si>
   <si>
     <t>已完成励磁调速PT及励变进线柜电压测量表计检查</t>
@@ -744,6 +732,9 @@
   </si>
   <si>
     <t>1号发电机励磁调节柜巡检任务已完成</t>
+  </si>
+  <si>
+    <t>已完成励磁变压器观察孔门检查</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1368,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1386,13 +1377,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1777,7 +1765,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.675" customWidth="1"/>
@@ -1807,16 +1795,16 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1825,11 +1813,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1838,11 +1826,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1851,11 +1839,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1864,13 +1852,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1879,11 +1867,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1892,11 +1880,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1905,13 +1893,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1920,11 +1908,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1933,11 +1921,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1946,13 +1934,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1961,11 +1949,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1974,13 +1962,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1989,11 +1977,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="4" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2002,11 +1990,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2015,13 +2003,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2030,11 +2018,11 @@
         <v>17</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="4" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2043,13 +2031,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2058,11 +2046,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="4" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2071,13 +2059,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2086,11 +2074,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="4" t="s">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2099,11 +2087,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="4" t="s">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2112,13 +2100,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2127,11 +2115,11 @@
         <v>24</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="4" t="s">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2140,11 +2128,11 @@
         <v>25</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4" t="s">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2153,13 +2141,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2168,2086 +2156,2064 @@
         <v>27</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="4" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" customHeight="1" spans="1:5">
+      <c r="E28" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1" spans="1:5">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="4" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>12</v>
+      <c r="E29" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="30" ht="39" customHeight="1" spans="1:5">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A31" s="2">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" ht="39" customHeight="1" spans="1:5">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" ht="72" customHeight="1" spans="1:5">
+      <c r="A32" s="2">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" ht="72" customHeight="1" spans="1:5">
+      <c r="E32" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" ht="55.5" customHeight="1" spans="1:5">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A34" s="2">
+        <v>34</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" ht="55.5" customHeight="1" spans="1:5">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" ht="39" customHeight="1" spans="1:5">
+      <c r="A35" s="2">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>12</v>
+      <c r="E35" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="36" ht="39" customHeight="1" spans="1:5">
       <c r="A36" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2"/>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3"/>
+      <c r="D36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="E36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A37" s="2">
+        <v>37</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" ht="39" customHeight="1" spans="1:5">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>9</v>
+      <c r="E37" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1" spans="1:5">
       <c r="A38" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>12</v>
+      <c r="C38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1" spans="1:5">
       <c r="A39" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2"/>
-      <c r="C39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>2</v>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1" spans="1:5">
       <c r="A40" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>12</v>
+      <c r="C40" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1" spans="1:5">
       <c r="A41" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2"/>
-      <c r="C41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>2</v>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1" spans="1:5">
       <c r="A42" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="4" t="s">
+      <c r="C42" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>12</v>
+      <c r="E42" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1" spans="1:5">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2"/>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>2</v>
+      <c r="E43" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1" spans="1:5">
       <c r="A44" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="4" t="s">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" ht="39" customHeight="1" spans="1:5">
+      <c r="A45" s="2">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A45" s="2">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" ht="39" customHeight="1" spans="1:5">
+      <c r="E45" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1" spans="1:5">
       <c r="A46" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2"/>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3"/>
+      <c r="D46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>2</v>
+      <c r="E46" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1" spans="1:5">
       <c r="A47" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="4" t="s">
+      <c r="C47" s="3"/>
+      <c r="D47" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" ht="39" customHeight="1" spans="1:5">
+      <c r="A48" s="2">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" ht="39" customHeight="1" spans="1:5">
+      <c r="E48" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" ht="22.5" customHeight="1" spans="1:5">
       <c r="A49" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="2"/>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="3"/>
+      <c r="D49" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>2</v>
+      <c r="E49" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1" spans="1:5">
       <c r="A50" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>9</v>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1" spans="1:5">
       <c r="A51" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="4" t="s">
+      <c r="C51" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>12</v>
+      <c r="E51" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1" spans="1:5">
       <c r="A52" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="2"/>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3"/>
+      <c r="D52" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>2</v>
+      <c r="E52" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1" spans="1:5">
       <c r="A53" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>9</v>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1" spans="1:5">
       <c r="A54" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="2"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>12</v>
+      <c r="C54" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1" spans="1:5">
       <c r="A55" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" s="2"/>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="3"/>
+      <c r="D55" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" ht="39" customHeight="1" spans="1:5">
+      <c r="A56" s="2">
+        <v>56</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A56" s="2">
-        <v>55</v>
-      </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="4" t="s">
+      <c r="C56" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" ht="39" customHeight="1" spans="1:5">
+      <c r="D56" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" ht="22.5" customHeight="1" spans="1:5">
       <c r="A57" s="2">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>2</v>
+      <c r="E57" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1" spans="1:5">
       <c r="A58" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="C58" s="3"/>
+      <c r="D58" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1" spans="1:5">
       <c r="A59" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="C59" s="3"/>
+      <c r="D59" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1" spans="1:5">
       <c r="A60" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B60" s="2"/>
-      <c r="C60" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>2</v>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1" spans="1:5">
       <c r="A61" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B61" s="2"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>9</v>
+      <c r="C61" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1" spans="1:5">
       <c r="A62" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B62" s="2"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>12</v>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1" spans="1:5">
       <c r="A63" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63" s="2"/>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" ht="39" customHeight="1" spans="1:5">
+      <c r="A64" s="2">
+        <v>65</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D64" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E63" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A64" s="2">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="4" t="s">
+      <c r="E64" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" ht="39" customHeight="1" spans="1:5">
+      <c r="A65" s="2">
+        <v>66</v>
+      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A65" s="2">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="4" t="s">
+      <c r="E65" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A66" s="2">
+        <v>67</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" ht="39" customHeight="1" spans="1:5">
-      <c r="A66" s="2">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2"/>
-      <c r="C66" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>2</v>
+      <c r="E66" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="67" ht="39" customHeight="1" spans="1:5">
       <c r="A67" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B67" s="2"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>9</v>
+      <c r="C67" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="68" ht="22.5" customHeight="1" spans="1:5">
       <c r="A68" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B68" s="2"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="4" t="s">
+      <c r="C68" s="3"/>
+      <c r="D68" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A69" s="2">
+        <v>70</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" ht="39" customHeight="1" spans="1:5">
-      <c r="A69" s="2">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2"/>
-      <c r="C69" s="4" t="s">
+      <c r="E69" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" ht="39" customHeight="1" spans="1:5">
+      <c r="A70" s="2">
+        <v>71</v>
+      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D70" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A70" s="2">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>9</v>
+      <c r="E70" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="71" ht="22.5" customHeight="1" spans="1:5">
       <c r="A71" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B71" s="2"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="4" t="s">
+      <c r="C71" s="3"/>
+      <c r="D71" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A72" s="2">
+        <v>73</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" ht="39" customHeight="1" spans="1:5">
-      <c r="A72" s="2">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2"/>
-      <c r="C72" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>2</v>
+      <c r="E72" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1" spans="1:5">
       <c r="A73" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B73" s="2"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>9</v>
+      <c r="C73" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1" spans="1:5">
       <c r="A74" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B74" s="2"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E74" s="3" t="s">
+      <c r="C74" s="3"/>
+      <c r="D74" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1" spans="1:5">
       <c r="A75" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75" s="2"/>
-      <c r="C75" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E75" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1" spans="1:5">
       <c r="A76" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76" s="2"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>12</v>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1" spans="1:5">
       <c r="A77" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B77" s="2"/>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="3"/>
+      <c r="D77" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" ht="39" customHeight="1" spans="1:5">
+      <c r="A78" s="2">
+        <v>79</v>
+      </c>
+      <c r="B78" s="2"/>
+      <c r="C78" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="E78" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" ht="39" customHeight="1" spans="1:5">
+      <c r="A79" s="2">
+        <v>80</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E77" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A78" s="2">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A79" s="2">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A80" s="2">
+        <v>81</v>
+      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" ht="39" customHeight="1" spans="1:5">
-      <c r="A80" s="2">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2"/>
-      <c r="C80" s="4" t="s">
+      <c r="E80" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A81" s="2">
+        <v>82</v>
+      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D81" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" ht="39" customHeight="1" spans="1:5">
-      <c r="A81" s="2">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>9</v>
+      <c r="E81" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="82" ht="22.5" customHeight="1" spans="1:5">
       <c r="A82" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B82" s="2"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>12</v>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1" spans="1:5">
       <c r="A83" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B83" s="2"/>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="3"/>
+      <c r="D83" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" ht="39" customHeight="1" spans="1:5">
+      <c r="A84" s="2">
+        <v>85</v>
+      </c>
+      <c r="B84" s="2"/>
+      <c r="C84" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D84" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A84" s="2">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>9</v>
+      <c r="E84" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1" spans="1:5">
       <c r="A85" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B85" s="2"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="4" t="s">
+      <c r="C85" s="3"/>
+      <c r="D85" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A86" s="2">
+        <v>87</v>
+      </c>
+      <c r="B86" s="2"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E85" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" ht="39" customHeight="1" spans="1:5">
-      <c r="A86" s="2">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2"/>
-      <c r="C86" s="4" t="s">
+      <c r="E86" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" ht="39" customHeight="1" spans="1:5">
+      <c r="A87" s="2">
+        <v>88</v>
+      </c>
+      <c r="B87" s="2"/>
+      <c r="C87" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D87" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A87" s="2">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>9</v>
+      <c r="E87" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1" spans="1:5">
       <c r="A88" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B88" s="2"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="4" t="s">
+      <c r="C88" s="3"/>
+      <c r="D88" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A89" s="2">
+        <v>90</v>
+      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" ht="39" customHeight="1" spans="1:5">
-      <c r="A89" s="2">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2"/>
-      <c r="C89" s="4" t="s">
+      <c r="E89" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" ht="39" customHeight="1" spans="1:5">
+      <c r="A90" s="2">
+        <v>91</v>
+      </c>
+      <c r="B90" s="2"/>
+      <c r="C90" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D90" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A90" s="2">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>9</v>
+      <c r="E90" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1" spans="1:5">
       <c r="A91" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B91" s="2"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="4" t="s">
+      <c r="C91" s="3"/>
+      <c r="D91" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A92" s="2">
+        <v>93</v>
+      </c>
+      <c r="B92" s="2"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" ht="39" customHeight="1" spans="1:5">
-      <c r="A92" s="2">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2"/>
-      <c r="C92" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>2</v>
+      <c r="E92" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1" spans="1:5">
       <c r="A93" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B93" s="2"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>9</v>
+      <c r="C93" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1" spans="1:5">
       <c r="A94" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B94" s="2"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>12</v>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="95" ht="22.5" customHeight="1" spans="1:5">
       <c r="A95" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B95" s="2"/>
-      <c r="C95" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>2</v>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1" spans="1:5">
       <c r="A96" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B96" s="2"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>9</v>
+      <c r="C96" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="97" ht="22.5" customHeight="1" spans="1:5">
       <c r="A97" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B97" s="2"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="C97" s="3"/>
+      <c r="D97" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1" spans="1:5">
       <c r="A98" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B98" s="2"/>
-      <c r="C98" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E98" s="3" t="s">
+      <c r="C98" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1" spans="1:5">
       <c r="A99" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B99" s="2"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="4" t="s">
+      <c r="C99" s="3"/>
+      <c r="D99" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" ht="39" customHeight="1" spans="1:5">
+      <c r="A100" s="2">
+        <v>101</v>
+      </c>
+      <c r="B100" s="2"/>
+      <c r="C100" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A100" s="2">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2"/>
-      <c r="C100" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="101" ht="22.5" customHeight="1" spans="1:5">
       <c r="A101" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B101" s="2"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="4" t="s">
+      <c r="C101" s="3"/>
+      <c r="D101" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A102" s="2">
+        <v>103</v>
+      </c>
+      <c r="B102" s="2"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" ht="39" customHeight="1" spans="1:5">
-      <c r="A102" s="2">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2"/>
-      <c r="C102" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>2</v>
+      <c r="E102" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="103" ht="22.5" customHeight="1" spans="1:5">
       <c r="A103" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B103" s="2"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>9</v>
+      <c r="C103" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="104" ht="22.5" customHeight="1" spans="1:5">
       <c r="A104" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B104" s="2"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>12</v>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="105" ht="22.5" customHeight="1" spans="1:5">
       <c r="A105" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B105" s="2"/>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="3"/>
+      <c r="D105" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" ht="39" customHeight="1" spans="1:5">
+      <c r="A106" s="2">
+        <v>107</v>
+      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D106" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E105" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A106" s="2">
-        <v>105</v>
-      </c>
-      <c r="B106" s="2"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>9</v>
+      <c r="E106" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="107" ht="22.5" customHeight="1" spans="1:5">
       <c r="A107" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B107" s="2"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="4" t="s">
+      <c r="C107" s="3"/>
+      <c r="D107" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A108" s="2">
+        <v>109</v>
+      </c>
+      <c r="B108" s="2"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" ht="39" customHeight="1" spans="1:5">
-      <c r="A108" s="2">
-        <v>107</v>
-      </c>
-      <c r="B108" s="2"/>
-      <c r="C108" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>2</v>
+      <c r="E108" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="109" ht="22.5" customHeight="1" spans="1:5">
       <c r="A109" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B109" s="2"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>9</v>
+      <c r="C109" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="110" ht="22.5" customHeight="1" spans="1:5">
       <c r="A110" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B110" s="2"/>
-      <c r="C110" s="5"/>
-      <c r="D110" s="4" t="s">
+      <c r="C110" s="3"/>
+      <c r="D110" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" ht="39" customHeight="1" spans="1:5">
+      <c r="A111" s="2">
+        <v>112</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E110" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A111" s="2">
-        <v>110</v>
-      </c>
-      <c r="B111" s="2"/>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="112" ht="22.5" customHeight="1" spans="1:5">
       <c r="A112" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B112" s="2"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="4" t="s">
+      <c r="C112" s="3"/>
+      <c r="D112" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E112" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="113" ht="39" customHeight="1" spans="1:5">
+      <c r="E112" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" ht="22.5" customHeight="1" spans="1:5">
       <c r="A113" s="2">
-        <v>112</v>
-      </c>
-      <c r="B113" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B113" s="2"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C113" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>2</v>
+      <c r="E113" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1" spans="1:5">
       <c r="A114" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B114" s="2"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>9</v>
+      <c r="C114" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="115" ht="22.5" customHeight="1" spans="1:5">
       <c r="A115" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B115" s="2"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>12</v>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1" spans="1:5">
       <c r="A116" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B116" s="2"/>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="3"/>
+      <c r="D116" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" ht="39" customHeight="1" spans="1:5">
+      <c r="A117" s="2">
+        <v>118</v>
+      </c>
+      <c r="B117" s="2"/>
+      <c r="C117" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D117" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A117" s="2">
-        <v>116</v>
-      </c>
-      <c r="B117" s="2"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>9</v>
+      <c r="E117" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="118" ht="22.5" customHeight="1" spans="1:5">
       <c r="A118" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B118" s="2"/>
-      <c r="C118" s="5"/>
-      <c r="D118" s="4" t="s">
+      <c r="C118" s="3"/>
+      <c r="D118" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A119" s="2">
+        <v>120</v>
+      </c>
+      <c r="B119" s="2"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E118" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" ht="39" customHeight="1" spans="1:5">
-      <c r="A119" s="2">
-        <v>118</v>
-      </c>
-      <c r="B119" s="2"/>
-      <c r="C119" s="4" t="s">
+      <c r="E119" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" ht="39" customHeight="1" spans="1:5">
+      <c r="A120" s="2">
+        <v>121</v>
+      </c>
+      <c r="B120" s="2"/>
+      <c r="C120" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D120" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E119" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A120" s="2">
-        <v>119</v>
-      </c>
-      <c r="B120" s="2"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>9</v>
+      <c r="E120" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1" spans="1:5">
       <c r="A121" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B121" s="2"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="4" t="s">
+      <c r="C121" s="3"/>
+      <c r="D121" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A122" s="2">
+        <v>123</v>
+      </c>
+      <c r="B122" s="2"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E121" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="122" ht="39" customHeight="1" spans="1:5">
-      <c r="A122" s="2">
-        <v>121</v>
-      </c>
-      <c r="B122" s="2"/>
-      <c r="C122" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D122" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>2</v>
+      <c r="E122" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="123" ht="22.5" customHeight="1" spans="1:5">
       <c r="A123" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B123" s="2"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>9</v>
+      <c r="C123" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="124" ht="22.5" customHeight="1" spans="1:5">
       <c r="A124" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B124" s="2"/>
-      <c r="C124" s="5"/>
-      <c r="D124" s="4" t="s">
+      <c r="C124" s="3"/>
+      <c r="D124" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" ht="39" customHeight="1" spans="1:5">
+      <c r="A125" s="2">
+        <v>126</v>
+      </c>
+      <c r="B125" s="2"/>
+      <c r="C125" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E124" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A125" s="2">
-        <v>124</v>
-      </c>
-      <c r="B125" s="2"/>
-      <c r="C125" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1" spans="1:5">
       <c r="A126" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B126" s="2"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="4" t="s">
+      <c r="C126" s="3"/>
+      <c r="D126" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A127" s="2">
+        <v>128</v>
+      </c>
+      <c r="B127" s="2"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E126" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" ht="39" customHeight="1" spans="1:5">
-      <c r="A127" s="2">
-        <v>126</v>
-      </c>
-      <c r="B127" s="2"/>
-      <c r="C127" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>2</v>
+      <c r="E127" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1" spans="1:5">
       <c r="A128" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B128" s="2"/>
-      <c r="C128" s="5"/>
-      <c r="D128" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>9</v>
+      <c r="C128" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="129" ht="22.5" customHeight="1" spans="1:5">
       <c r="A129" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B129" s="2"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>12</v>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="130" ht="22.5" customHeight="1" spans="1:5">
       <c r="A130" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B130" s="2"/>
-      <c r="C130" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>2</v>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="131" ht="22.5" customHeight="1" spans="1:5">
       <c r="A131" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B131" s="2"/>
-      <c r="C131" s="5"/>
-      <c r="D131" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>9</v>
+      <c r="C131" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="132" ht="22.5" customHeight="1" spans="1:5">
       <c r="A132" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B132" s="2"/>
-      <c r="C132" s="5"/>
-      <c r="D132" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>12</v>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="133" ht="22.5" customHeight="1" spans="1:5">
       <c r="A133" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B133" s="2"/>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="3"/>
+      <c r="D133" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" ht="39" customHeight="1" spans="1:5">
+      <c r="A134" s="2">
+        <v>135</v>
+      </c>
+      <c r="B134" s="2"/>
+      <c r="C134" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="D134" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E133" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="134" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A134" s="2">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2"/>
-      <c r="C134" s="5"/>
-      <c r="D134" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>9</v>
+      <c r="E134" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="135" ht="22.5" customHeight="1" spans="1:5">
       <c r="A135" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B135" s="2"/>
-      <c r="C135" s="5"/>
-      <c r="D135" s="4" t="s">
+      <c r="C135" s="3"/>
+      <c r="D135" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A136" s="2">
+        <v>137</v>
+      </c>
+      <c r="B136" s="2"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E135" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="136" ht="39" customHeight="1" spans="1:5">
-      <c r="A136" s="2">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2"/>
-      <c r="C136" s="4" t="s">
+      <c r="E136" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" ht="39" customHeight="1" spans="1:5">
+      <c r="A137" s="2">
+        <v>138</v>
+      </c>
+      <c r="B137" s="2"/>
+      <c r="C137" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="D137" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E136" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A137" s="2">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2"/>
-      <c r="C137" s="5"/>
-      <c r="D137" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>9</v>
+      <c r="E137" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="138" ht="22.5" customHeight="1" spans="1:5">
       <c r="A138" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B138" s="2"/>
-      <c r="C138" s="5"/>
-      <c r="D138" s="4" t="s">
+      <c r="C138" s="3"/>
+      <c r="D138" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A139" s="2">
+        <v>140</v>
+      </c>
+      <c r="B139" s="2"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E138" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" ht="39" customHeight="1" spans="1:5">
-      <c r="A139" s="2">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2"/>
-      <c r="C139" s="4" t="s">
+      <c r="E139" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" ht="39" customHeight="1" spans="1:5">
+      <c r="A140" s="2">
+        <v>141</v>
+      </c>
+      <c r="B140" s="2"/>
+      <c r="C140" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D139" s="4" t="s">
+      <c r="D140" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E139" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A140" s="2">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>9</v>
+      <c r="E140" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="141" ht="22.5" customHeight="1" spans="1:5">
       <c r="A141" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B141" s="2"/>
-      <c r="C141" s="5"/>
-      <c r="D141" s="4" t="s">
+      <c r="C141" s="3"/>
+      <c r="D141" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A142" s="2">
+        <v>143</v>
+      </c>
+      <c r="B142" s="2"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E141" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="142" ht="39" customHeight="1" spans="1:5">
-      <c r="A142" s="2">
-        <v>141</v>
-      </c>
-      <c r="B142" s="2"/>
-      <c r="C142" s="4" t="s">
+      <c r="E142" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" ht="39" customHeight="1" spans="1:5">
+      <c r="A143" s="2">
+        <v>144</v>
+      </c>
+      <c r="B143" s="2"/>
+      <c r="C143" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D142" s="4" t="s">
+      <c r="D143" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E142" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="143" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A143" s="2">
-        <v>142</v>
-      </c>
-      <c r="B143" s="2"/>
-      <c r="C143" s="5"/>
-      <c r="D143" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>9</v>
+      <c r="E143" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="144" ht="22.5" customHeight="1" spans="1:5">
       <c r="A144" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B144" s="2"/>
-      <c r="C144" s="5"/>
-      <c r="D144" s="4" t="s">
+      <c r="C144" s="3"/>
+      <c r="D144" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A145" s="2">
+        <v>146</v>
+      </c>
+      <c r="B145" s="2"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E144" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" ht="39" customHeight="1" spans="1:5">
-      <c r="A145" s="2">
-        <v>144</v>
-      </c>
-      <c r="B145" s="2"/>
-      <c r="C145" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>2</v>
+      <c r="E145" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="146" ht="22.5" customHeight="1" spans="1:5">
       <c r="A146" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B146" s="2"/>
-      <c r="C146" s="5"/>
-      <c r="D146" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>9</v>
+      <c r="C146" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="147" ht="22.5" customHeight="1" spans="1:5">
       <c r="A147" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B147" s="2"/>
-      <c r="C147" s="5"/>
-      <c r="D147" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="E147" s="3" t="s">
+      <c r="C147" s="3"/>
+      <c r="D147" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="148" ht="22.5" customHeight="1" spans="1:5">
       <c r="A148" s="2">
-        <v>147</v>
-      </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D148" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D148" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E148" s="3" t="s">
+      <c r="E148" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="149" ht="22.5" customHeight="1" spans="1:5">
       <c r="A149" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B149" s="2"/>
-      <c r="C149" s="5"/>
-      <c r="D149" s="4" t="s">
+      <c r="C149" s="3"/>
+      <c r="D149" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E149" s="3" t="s">
-        <v>12</v>
+      <c r="E149" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="150" ht="22.5" customHeight="1" spans="1:5">
       <c r="A150" s="2">
-        <v>149</v>
-      </c>
-      <c r="B150" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B150" s="2"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C150" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>2</v>
+      <c r="E150" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="151" ht="22.5" customHeight="1" spans="1:5">
       <c r="A151" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B151" s="2"/>
-      <c r="C151" s="5"/>
-      <c r="D151" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>9</v>
+      <c r="C151" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="152" ht="22.5" customHeight="1" spans="1:5">
       <c r="A152" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B152" s="2"/>
-      <c r="C152" s="5"/>
-      <c r="D152" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>12</v>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="153" ht="22.5" customHeight="1" spans="1:5">
       <c r="A153" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B153" s="2"/>
-      <c r="C153" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>2</v>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="154" ht="22.5" customHeight="1" spans="1:5">
       <c r="A154" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B154" s="2"/>
-      <c r="C154" s="5"/>
-      <c r="D154" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>9</v>
+      <c r="C154" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="155" ht="22.5" customHeight="1" spans="1:5">
       <c r="A155" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B155" s="2"/>
-      <c r="C155" s="5"/>
-      <c r="D155" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>12</v>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="156" ht="22.5" customHeight="1" spans="1:5">
       <c r="A156" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B156" s="2"/>
-      <c r="C156" s="4" t="s">
+      <c r="C156" s="3"/>
+      <c r="D156" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" ht="39" customHeight="1" spans="1:5">
+      <c r="A157" s="2">
+        <v>158</v>
+      </c>
+      <c r="B157" s="2"/>
+      <c r="C157" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="D157" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E156" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="157" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A157" s="2">
-        <v>156</v>
-      </c>
-      <c r="B157" s="2"/>
-      <c r="C157" s="5"/>
-      <c r="D157" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>9</v>
+      <c r="E157" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="158" ht="22.5" customHeight="1" spans="1:5">
       <c r="A158" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B158" s="2"/>
-      <c r="C158" s="5"/>
-      <c r="D158" s="4" t="s">
+      <c r="C158" s="3"/>
+      <c r="D158" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A159" s="2">
+        <v>160</v>
+      </c>
+      <c r="B159" s="2"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E158" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="159" ht="39" customHeight="1" spans="1:5">
-      <c r="A159" s="2">
-        <v>158</v>
-      </c>
-      <c r="B159" s="2"/>
-      <c r="C159" s="4" t="s">
+      <c r="E159" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" ht="39" customHeight="1" spans="1:5">
+      <c r="A160" s="2">
+        <v>161</v>
+      </c>
+      <c r="B160" s="2"/>
+      <c r="C160" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D159" s="4" t="s">
+      <c r="D160" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E159" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="160" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A160" s="2">
-        <v>159</v>
-      </c>
-      <c r="B160" s="2"/>
-      <c r="C160" s="5"/>
-      <c r="D160" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>9</v>
+      <c r="E160" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="161" ht="22.5" customHeight="1" spans="1:5">
       <c r="A161" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B161" s="2"/>
-      <c r="C161" s="5"/>
-      <c r="D161" s="4" t="s">
+      <c r="C161" s="3"/>
+      <c r="D161" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" ht="22.5" customHeight="1" spans="1:5">
+      <c r="A162" s="2">
+        <v>163</v>
+      </c>
+      <c r="B162" s="2"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E161" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="162" ht="39" customHeight="1" spans="1:5">
-      <c r="A162" s="2">
-        <v>161</v>
-      </c>
-      <c r="B162" s="2"/>
-      <c r="C162" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D162" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>2</v>
+      <c r="E162" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="163" ht="22.5" customHeight="1" spans="1:5">
       <c r="A163" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B163" s="2"/>
-      <c r="C163" s="5"/>
-      <c r="D163" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>9</v>
+      <c r="C163" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="164" ht="22.5" customHeight="1" spans="1:5">
       <c r="A164" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B164" s="2"/>
-      <c r="C164" s="5"/>
-      <c r="D164" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>12</v>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="165" ht="22.5" customHeight="1" spans="1:5">
       <c r="A165" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B165" s="2"/>
-      <c r="C165" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D165" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>2</v>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="166" ht="22.5" customHeight="1" spans="1:5">
       <c r="A166" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B166" s="2"/>
-      <c r="C166" s="5"/>
-      <c r="D166" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>9</v>
+      <c r="C166" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="167" ht="22.5" customHeight="1" spans="1:5">
       <c r="A167" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B167" s="2"/>
-      <c r="C167" s="5"/>
-      <c r="D167" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>12</v>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="168" ht="22.5" customHeight="1" spans="1:5">
       <c r="A168" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B168" s="2"/>
-      <c r="C168" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>2</v>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1" spans="1:5">
       <c r="A169" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B169" s="2"/>
-      <c r="C169" s="5"/>
-      <c r="D169" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>9</v>
+      <c r="C169" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="170" ht="22.5" customHeight="1" spans="1:5">
       <c r="A170" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B170" s="2"/>
-      <c r="C170" s="5"/>
-      <c r="D170" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>12</v>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="171" ht="22.5" customHeight="1" spans="1:5">
       <c r="A171" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B171" s="2"/>
-      <c r="C171" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>2</v>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="172" ht="22.5" customHeight="1" spans="1:5">
       <c r="A172" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B172" s="2"/>
-      <c r="C172" s="5"/>
-      <c r="D172" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>9</v>
+      <c r="C172" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="173" ht="22.5" customHeight="1" spans="1:5">
       <c r="A173" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B173" s="2"/>
-      <c r="C173" s="5"/>
-      <c r="D173" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="E173" s="3" t="s">
-        <v>12</v>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="174" ht="22.5" customHeight="1" spans="1:5">
       <c r="A174" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B174" s="2"/>
-      <c r="C174" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="D174" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>2</v>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1" spans="1:5">
       <c r="A175" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B175" s="2"/>
-      <c r="C175" s="5"/>
-      <c r="D175" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>9</v>
+      <c r="C175" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="176" ht="22.5" customHeight="1" spans="1:5">
       <c r="A176" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B176" s="2"/>
-      <c r="C176" s="5"/>
-      <c r="D176" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="E176" s="3" t="s">
-        <v>12</v>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="177" ht="22.5" customHeight="1" spans="1:5">
       <c r="A177" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B177" s="2"/>
-      <c r="C177" s="4" t="s">
+      <c r="C177" s="3"/>
+      <c r="D177" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E177" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" ht="16.5" spans="1:5">
+      <c r="D178" t="s">
         <v>235</v>
       </c>
-      <c r="D177" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="178" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A178" s="2">
-        <v>177</v>
-      </c>
-      <c r="B178" s="2"/>
-      <c r="C178" s="5"/>
-      <c r="D178" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="179" ht="22.5" customHeight="1" spans="1:5">
-      <c r="A179" s="2">
-        <v>178</v>
-      </c>
-      <c r="B179" s="2"/>
-      <c r="C179" s="5"/>
-      <c r="D179" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="E179" s="3" t="s">
+      <c r="E178" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4255,7 +4221,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 B2:E179" numberStoredAsText="1"/>
+    <ignoredError sqref="D84:E84 B84 B60:E66 B58:C59 B57:E57 D56:E56 B56 B31:E55 B29:C30 B28:E28 E27 B27 B2:E26 B67 E67 B68:E68 B69:C69 E69 B70:E83 B159:E174 B175:C175 E175 B176:D177 E158 B158:C158 D157:E157 B157 B149:E156 C148:E148 B121:C121 E121 B122:E133 B134:C135 E134:E135 B136:E147 D120:E120 B120 B86:E119 E85 B85:C85 A1:E1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>